--- a/Portifolio.xlsx
+++ b/Portifolio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gusta\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB6C6480-867C-4930-BF75-79EF361EFDA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CDD1FB8-D0FE-4D16-994D-D2A57CCD1A52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B5D9E45B-8D16-461F-A821-93BE91145450}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{B5D9E45B-8D16-461F-A821-93BE91145450}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,18 @@
     <sheet name="Painel" sheetId="7" r:id="rId4"/>
     <sheet name="Dashboard" sheetId="8" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlchart.v5.0" hidden="1">Base!$I$12</definedName>
+    <definedName name="_xlchart.v5.1" hidden="1">Base!$I$13:$I$16</definedName>
+    <definedName name="_xlchart.v5.2" hidden="1">Base!$J$11</definedName>
+    <definedName name="_xlchart.v5.3" hidden="1">Base!$J$12</definedName>
+    <definedName name="_xlchart.v5.4" hidden="1">Base!$J$13:$J$16</definedName>
+    <definedName name="_xlchart.v5.5" hidden="1">Dashboard!$A$10</definedName>
+    <definedName name="_xlchart.v5.6" hidden="1">Dashboard!$A$11</definedName>
+    <definedName name="_xlchart.v5.7" hidden="1">Base!$I$12:$I$16</definedName>
+    <definedName name="_xlchart.v5.8" hidden="1">Dashboard!$A$10</definedName>
+    <definedName name="_xlchart.v5.9" hidden="1">Dashboard!$A$11</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
     <pivotCache cacheId="0" r:id="rId6"/>
@@ -46,7 +58,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -68,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="41">
   <si>
     <t xml:space="preserve">Data </t>
   </si>
@@ -183,6 +195,15 @@
   <si>
     <t>% acumulada</t>
   </si>
+  <si>
+    <t>Datas</t>
+  </si>
+  <si>
+    <t>Entregas</t>
+  </si>
+  <si>
+    <t>RápidLog - Dashboard de entregas</t>
+  </si>
 </sst>
 </file>
 
@@ -192,7 +213,7 @@
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -230,8 +251,44 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="48"/>
+      <color theme="0"/>
+      <name val="BankGothic Md BT"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <color theme="0"/>
+      <name val="Bookman Old Style"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="36"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -274,8 +331,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -298,12 +373,148 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -339,11 +550,91 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="9" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="9" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="10" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="10" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="10" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="8" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="10" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="10" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="10" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="10" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="10" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="10" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Porcentagem" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="6">
     <dxf>
@@ -494,12 +785,27 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent1"/>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="75000"/>
+              </a:schemeClr>
             </a:solidFill>
-            <a:ln>
+            <a:ln w="41275">
               <a:noFill/>
             </a:ln>
-            <a:effectLst/>
+            <a:effectLst>
+              <a:glow rad="139700">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="75000"/>
+                  <a:alpha val="40000"/>
+                </a:schemeClr>
+              </a:glow>
+              <a:outerShdw dist="50800" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="10000"/>
+                  <a:lumOff val="90000"/>
+                </a:schemeClr>
+              </a:outerShdw>
+            </a:effectLst>
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dPt>
@@ -508,14 +814,27 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="bg2">
+                <a:schemeClr val="accent1">
                   <a:lumMod val="75000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:ln>
+              <a:ln w="41275">
                 <a:noFill/>
               </a:ln>
-              <a:effectLst/>
+              <a:effectLst>
+                <a:glow rad="139700">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="75000"/>
+                    <a:alpha val="40000"/>
+                  </a:schemeClr>
+                </a:glow>
+                <a:outerShdw dist="50800" dir="5400000" algn="ctr" rotWithShape="0">
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="10000"/>
+                    <a:lumOff val="90000"/>
+                  </a:schemeClr>
+                </a:outerShdw>
+              </a:effectLst>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -529,14 +848,27 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent4">
-                  <a:lumMod val="50000"/>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="75000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:ln>
+              <a:ln w="41275">
                 <a:noFill/>
               </a:ln>
-              <a:effectLst/>
+              <a:effectLst>
+                <a:glow rad="139700">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="75000"/>
+                    <a:alpha val="40000"/>
+                  </a:schemeClr>
+                </a:glow>
+                <a:outerShdw dist="50800" dir="5400000" algn="ctr" rotWithShape="0">
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="10000"/>
+                    <a:lumOff val="90000"/>
+                  </a:schemeClr>
+                </a:outerShdw>
+              </a:effectLst>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -550,14 +882,27 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent5">
+                <a:schemeClr val="accent1">
                   <a:lumMod val="75000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:ln>
+              <a:ln w="41275">
                 <a:noFill/>
               </a:ln>
-              <a:effectLst/>
+              <a:effectLst>
+                <a:glow rad="139700">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="75000"/>
+                    <a:alpha val="40000"/>
+                  </a:schemeClr>
+                </a:glow>
+                <a:outerShdw dist="50800" dir="5400000" algn="ctr" rotWithShape="0">
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="10000"/>
+                    <a:lumOff val="90000"/>
+                  </a:schemeClr>
+                </a:outerShdw>
+              </a:effectLst>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -572,14 +917,26 @@
             <c:spPr>
               <a:solidFill>
                 <a:schemeClr val="accent1">
-                  <a:lumMod val="20000"/>
-                  <a:lumOff val="80000"/>
+                  <a:lumMod val="75000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:ln>
+              <a:ln w="41275">
                 <a:noFill/>
               </a:ln>
-              <a:effectLst/>
+              <a:effectLst>
+                <a:glow rad="139700">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="75000"/>
+                    <a:alpha val="40000"/>
+                  </a:schemeClr>
+                </a:glow>
+                <a:outerShdw dist="50800" dir="5400000" algn="ctr" rotWithShape="0">
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="10000"/>
+                    <a:lumOff val="90000"/>
+                  </a:schemeClr>
+                </a:outerShdw>
+              </a:effectLst>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -593,14 +950,27 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="50000"/>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="75000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:ln>
+              <a:ln w="41275">
                 <a:noFill/>
               </a:ln>
-              <a:effectLst/>
+              <a:effectLst>
+                <a:glow rad="139700">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="75000"/>
+                    <a:alpha val="40000"/>
+                  </a:schemeClr>
+                </a:glow>
+                <a:outerShdw dist="50800" dir="5400000" algn="ctr" rotWithShape="0">
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="10000"/>
+                    <a:lumOff val="90000"/>
+                  </a:schemeClr>
+                </a:outerShdw>
+              </a:effectLst>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -614,15 +984,27 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent3">
-                  <a:lumMod val="60000"/>
-                  <a:lumOff val="40000"/>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="75000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:ln>
+              <a:ln w="41275">
                 <a:noFill/>
               </a:ln>
-              <a:effectLst/>
+              <a:effectLst>
+                <a:glow rad="139700">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="75000"/>
+                    <a:alpha val="40000"/>
+                  </a:schemeClr>
+                </a:glow>
+                <a:outerShdw dist="50800" dir="5400000" algn="ctr" rotWithShape="0">
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="10000"/>
+                    <a:lumOff val="90000"/>
+                  </a:schemeClr>
+                </a:outerShdw>
+              </a:effectLst>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -636,14 +1018,27 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent2">
+                <a:schemeClr val="accent1">
                   <a:lumMod val="75000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:ln>
+              <a:ln w="41275">
                 <a:noFill/>
               </a:ln>
-              <a:effectLst/>
+              <a:effectLst>
+                <a:glow rad="139700">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="75000"/>
+                    <a:alpha val="40000"/>
+                  </a:schemeClr>
+                </a:glow>
+                <a:outerShdw dist="50800" dir="5400000" algn="ctr" rotWithShape="0">
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="10000"/>
+                    <a:lumOff val="90000"/>
+                  </a:schemeClr>
+                </a:outerShdw>
+              </a:effectLst>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -666,7 +1061,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="bg1"/>
                     </a:solidFill>
@@ -678,6 +1073,7 @@
                 <a:endParaRPr lang="pt-BR"/>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="outEnd"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="1"/>
             <c:showCatName val="0"/>
@@ -808,11 +1204,11 @@
           <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:ln>
                   <a:noFill/>
                 </a:ln>
@@ -829,7 +1225,7 @@
         </c:txPr>
         <c:crossAx val="1072960367"/>
         <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
+        <c:auto val="0"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
         <c:noMultiLvlLbl val="0"/>
@@ -913,6 +1309,306 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.21473463894999306"/>
+          <c:y val="0.1341783711111264"/>
+          <c:w val="0.61589110539556025"/>
+          <c:h val="0.76316559449005139"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Base!$J$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Quantidade</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:effectLst>
+              <a:outerShdw blurRad="63500" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="75000"/>
+                  <a:alpha val="40000"/>
+                </a:schemeClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="63500" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="75000"/>
+                    <a:alpha val="40000"/>
+                  </a:schemeClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-DCAF-4E54-AC17-7D9ACE6D76DD}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="63500" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="75000"/>
+                    <a:alpha val="40000"/>
+                  </a:schemeClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-DCAF-4E54-AC17-7D9ACE6D76DD}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="63500" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="75000"/>
+                    <a:alpha val="40000"/>
+                  </a:schemeClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-DCAF-4E54-AC17-7D9ACE6D76DD}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="pt-BR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="inEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="1"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Base!$I$8:$I$10</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>PENDENTE</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>DEVOLVIDO</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>ENTREGUE</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Base!$J$8:$J$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>61</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-DCAF-4E54-AC17-7D9ACE6D76DD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="inEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="0"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:alpha val="78000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
     <c:title>
       <c:tx>
         <c:rich>
@@ -930,14 +1626,9 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>Status</a:t>
+              <a:rPr lang="pt-BR"/>
+              <a:t>% Receita por Cidade</a:t>
             </a:r>
-            <a:r>
-              <a:rPr lang="en-US" baseline="0"/>
-              <a:t> Entregas</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -969,98 +1660,55 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
-      <c:pieChart>
-        <c:varyColors val="1"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.20528710865075464"/>
+          <c:y val="0.15572820825054431"/>
+          <c:w val="0.70629610787563202"/>
+          <c:h val="0.64149551648124636"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Base!$J$7</c:f>
+              <c:f>Base!$J$12</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Quantidade</c:v>
+                  <c:v>Receita</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln>
-              <a:solidFill>
-                <a:schemeClr val="bg1">
-                  <a:alpha val="0"/>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="38100">
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="63500" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="10000"/>
+                  <a:lumOff val="90000"/>
+                  <a:alpha val="40000"/>
                 </a:schemeClr>
-              </a:solidFill>
-            </a:ln>
+              </a:outerShdw>
+            </a:effectLst>
           </c:spPr>
-          <c:dPt>
-            <c:idx val="0"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="bg1">
-                    <a:alpha val="0"/>
-                  </a:schemeClr>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-DCAF-4E54-AC17-7D9ACE6D76DD}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="1"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="bg1">
-                    <a:alpha val="0"/>
-                  </a:schemeClr>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-DCAF-4E54-AC17-7D9ACE6D76DD}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="2"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="bg1">
-                    <a:alpha val="0"/>
-                  </a:schemeClr>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-DCAF-4E54-AC17-7D9ACE6D76DD}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
+          <c:invertIfNegative val="0"/>
           <c:dLbls>
             <c:spPr>
               <a:noFill/>
@@ -1076,7 +1724,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="bg1"/>
                     </a:solidFill>
@@ -1089,54 +1737,76 @@
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="1"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
             <c:showSerName val="0"/>
-            <c:showPercent val="1"/>
+            <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
             <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Base!$I$8:$I$10</c:f>
+              <c:f>Base!$I$13:$I$16</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>PENDENTE</c:v>
+                  <c:v>Campinas</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>DEVOLVIDO</c:v>
+                  <c:v>São Paulo</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>ENTREGUE</c:v>
+                  <c:v>Barueri</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Jandira</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Base!$J$8:$J$10</c:f>
+              <c:f>Base!$J$13:$J$16</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:formatCode>_("R$"* #,##0.00_);_("R$"* \(#,##0.00\);_("R$"* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>61</c:v>
+                  <c:v>26530700</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>52</c:v>
+                  <c:v>14040800</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>61</c:v>
+                  <c:v>4444500</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3721920</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-DCAF-4E54-AC17-7D9ACE6D76DD}"/>
+              <c16:uniqueId val="{00000000-DCF8-4E60-B455-8A836CFC13F6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1147,10 +1817,965 @@
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
-          <c:showLeaderLines val="0"/>
         </c:dLbls>
-        <c:firstSliceAng val="0"/>
-      </c:pieChart>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1996041807"/>
+        <c:axId val="1928271119"/>
+      </c:barChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Base!$K$12</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>% acumulada</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Base!$I$13:$I$16</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Campinas</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>São Paulo</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Barueri</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Jandira</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Base!$K$13:$K$16</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.54435437540215093</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.83244217233726836</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.92363399997373707</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-DCF8-4E60-B455-8A836CFC13F6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="135223663"/>
+        <c:axId val="1582554223"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1996041807"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1500" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="bg1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1928271119"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1928271119"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="_(&quot;R$&quot;* #,##0.00_);_(&quot;R$&quot;* \(#,##0.00\);_(&quot;R$&quot;* &quot;-&quot;??_);_(@_)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1500" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="bg1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1996041807"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1582554223"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1500" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="bg1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="135223663"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:catAx>
+        <c:axId val="135223663"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1582554223"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="95000"/>
+        <a:lumOff val="5000"/>
+      </a:schemeClr>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:solidFill>
+            <a:schemeClr val="bg1"/>
+          </a:solidFill>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Base!$J$18</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Entregas</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="sq">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+              <a:headEnd type="none"/>
+              <a:tailEnd type="triangle"/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="63500" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="10000"/>
+                  <a:lumOff val="90000"/>
+                  <a:alpha val="40000"/>
+                </a:schemeClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Base!$I$19:$I$90</c:f>
+              <c:numCache>
+                <c:formatCode>m/d/yyyy</c:formatCode>
+                <c:ptCount val="72"/>
+                <c:pt idx="0">
+                  <c:v>46063</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46061</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46070</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46037</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46035</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46105</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46108</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46077</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46096</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46093</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46041</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>46034</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>46088</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>46051</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>46049</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>46110</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46040</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>46069</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>46087</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>46044</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>46053</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46048</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>46111</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>46054</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>46057</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>46103</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>46074</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>46045</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>46082</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>46043</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>46083</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>46042</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>46085</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>46039</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>46068</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>46109</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46058</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>46060</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>46067</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46078</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>46073</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>46104</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>46071</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>46092</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46059</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>46066</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>46086</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>46094</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>46099</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46072</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46056</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46047</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46055</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46091</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46100</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46101</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46036</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46098</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>46079</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>46107</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>46065</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>46064</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>46038</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>46106</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>46046</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>46076</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Base!$J$19:$J$90</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="72"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-83F1-445B-A5C4-00B54C188198}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="173364015"/>
+        <c:axId val="173364975"/>
+      </c:lineChart>
+      <c:dateAx>
+        <c:axId val="173364015"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="m/d/yyyy" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="bg1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="173364975"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="days"/>
+      </c:dateAx>
+      <c:valAx>
+        <c:axId val="173364975"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="bg1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="173364015"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -1190,7 +2815,7 @@
       <a:pPr>
         <a:defRPr>
           <a:solidFill>
-            <a:schemeClr val="bg1"/>
+            <a:schemeClr val="tx1"/>
           </a:solidFill>
         </a:defRPr>
       </a:pPr>
@@ -1246,6 +2871,86 @@
 </file>
 
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -1789,7 +3494,538 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="261">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="dkDnDiag">
+        <a:fgClr>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:alpha val="75000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="317500" algn="ctr" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="25000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="88900" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="20000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+      <a:scene3d>
+        <a:camera prst="orthographicFront"/>
+        <a:lightRig rig="threePt" dir="t"/>
+      </a:scene3d>
+      <a:sp3d prstMaterial="matte"/>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:alpha val="78000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1800" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -1846,7 +4082,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="1000" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
@@ -1897,13 +4133,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -1914,19 +4143,12 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="25400">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
+    <cs:fillRef idx="1"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -1964,7 +4186,7 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
+    <cs:fillRef idx="1"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -2007,23 +4229,22 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -2128,8 +4349,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -2261,12 +4482,315 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
@@ -2275,6 +4799,218 @@
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -2312,15 +5048,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>379730</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>61854</xdr:rowOff>
+      <xdr:colOff>378378</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>68949</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>349624</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>143435</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>181151</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>67204</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2349,16 +5085,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>22187</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>66253</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>79870</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>268941</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>35859</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>415636</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>178364</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2380,6 +5116,82 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>346364</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>157819</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>155372</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>156073</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Gráfico 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{863B532D-6EA9-43CE-92AD-BA7F8F9547CE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>551618</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>1746</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>290945</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Gráfico 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8432ECC-43E8-45C7-AAD5-FDC2167245B3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4258,21 +7070,44 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="438" row="9">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{170AB4D8-E4C8-485A-911A-685E3E184304}">
+  <we:reference id="wa200009404" version="1.0.0.8" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="wa200009404" version="1.0.0.8" store="en-US" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;932f3d10-85ec-42c0-a641-cc78149f7572&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD543FCA-233A-4DE5-A9D7-D080F63BC994}">
   <dimension ref="A1:K175"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.54296875" customWidth="1"/>
+    <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5546875" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="12.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.6328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4298,7 +7133,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>46063</v>
       </c>
@@ -4325,7 +7160,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>46061</v>
       </c>
@@ -4352,7 +7187,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>46070</v>
       </c>
@@ -4379,7 +7214,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>46063</v>
       </c>
@@ -4406,7 +7241,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>46037</v>
       </c>
@@ -4427,7 +7262,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>46035</v>
       </c>
@@ -4454,7 +7289,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>46061</v>
       </c>
@@ -4483,7 +7318,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>46105</v>
       </c>
@@ -4511,7 +7346,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>46108</v>
       </c>
@@ -4539,7 +7374,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>46077</v>
       </c>
@@ -4560,7 +7395,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>46061</v>
       </c>
@@ -4580,17 +7415,17 @@
       <c r="F12" t="s">
         <v>17</v>
       </c>
-      <c r="I12" t="s">
+      <c r="I12" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="J12" t="s">
+      <c r="J12" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="K12" t="s">
+      <c r="K12" s="20" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>46096</v>
       </c>
@@ -4610,16 +7445,19 @@
       <c r="F13" t="s">
         <v>18</v>
       </c>
-      <c r="I13" t="str" cm="1">
-        <f t="array" ref="I13:I16">_xlfn.UNIQUE(Tabela2[Cidade],0,0)</f>
-        <v>Barueri</v>
-      </c>
-      <c r="J13" s="17">
+      <c r="I13" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="J13" s="22">
         <f>SUMIF(Tabela2[[#All],[Cidade]],I13,Tabela2[[#All],[Frete(R$)]])</f>
-        <v>4444500</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+        <v>26530700</v>
+      </c>
+      <c r="K13" s="26">
+        <f>J13/SUM($J$13:$J$16)</f>
+        <v>0.54435437540215093</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>46093</v>
       </c>
@@ -4639,15 +7477,19 @@
       <c r="F14" t="s">
         <v>18</v>
       </c>
-      <c r="I14" t="str">
-        <v>São Paulo</v>
-      </c>
-      <c r="J14" s="17">
+      <c r="I14" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="J14" s="24">
         <f>SUMIF(Tabela2[[#All],[Cidade]],I14,Tabela2[[#All],[Frete(R$)]])</f>
         <v>14040800</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="K14" s="27">
+        <f>K13+J14/SUM($J$13:$J$16)</f>
+        <v>0.83244217233726836</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>46041</v>
       </c>
@@ -4667,15 +7509,19 @@
       <c r="F15" t="s">
         <v>19</v>
       </c>
-      <c r="I15" t="str">
-        <v>Jandira</v>
-      </c>
-      <c r="J15" s="17">
+      <c r="I15" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="J15" s="22">
         <f>SUMIF(Tabela2[[#All],[Cidade]],I15,Tabela2[[#All],[Frete(R$)]])</f>
-        <v>3721920</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+        <v>4444500</v>
+      </c>
+      <c r="K15" s="27">
+        <f t="shared" ref="K15:K16" si="0">K14+J15/SUM($J$13:$J$16)</f>
+        <v>0.92363399997373707</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>46034</v>
       </c>
@@ -4695,15 +7541,19 @@
       <c r="F16" t="s">
         <v>17</v>
       </c>
-      <c r="I16" t="str">
-        <v>Campinas</v>
-      </c>
-      <c r="J16" s="17">
+      <c r="I16" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="J16" s="25">
         <f>SUMIF(Tabela2[[#All],[Cidade]],I16,Tabela2[[#All],[Frete(R$)]])</f>
-        <v>26530700</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+        <v>3721920</v>
+      </c>
+      <c r="K16" s="27">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>46088</v>
       </c>
@@ -4724,7 +7574,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>46108</v>
       </c>
@@ -4744,8 +7594,14 @@
       <c r="F18" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I18" t="s">
+        <v>38</v>
+      </c>
+      <c r="J18" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>46051</v>
       </c>
@@ -4765,8 +7621,15 @@
       <c r="F19" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I19" s="1">
+        <v>46063</v>
+      </c>
+      <c r="J19">
+        <f>COUNTIF($A$2:$A$10000,I19)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>46049</v>
       </c>
@@ -4786,8 +7649,15 @@
       <c r="F20" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I20" s="1">
+        <v>46061</v>
+      </c>
+      <c r="J20">
+        <f t="shared" ref="J20:J83" si="1">COUNTIF($A$2:$A$10000,I20)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>46110</v>
       </c>
@@ -4807,8 +7677,15 @@
       <c r="F21" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I21" s="1">
+        <v>46070</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>46040</v>
       </c>
@@ -4828,8 +7705,15 @@
       <c r="F22" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I22" s="1">
+        <v>46037</v>
+      </c>
+      <c r="J22">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>46040</v>
       </c>
@@ -4849,8 +7733,15 @@
       <c r="F23" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I23" s="1">
+        <v>46035</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>46069</v>
       </c>
@@ -4870,8 +7761,15 @@
       <c r="F24" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I24" s="1">
+        <v>46105</v>
+      </c>
+      <c r="J24">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>46087</v>
       </c>
@@ -4891,8 +7789,15 @@
       <c r="F25" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I25" s="1">
+        <v>46108</v>
+      </c>
+      <c r="J25">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>46040</v>
       </c>
@@ -4912,8 +7817,15 @@
       <c r="F26" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I26" s="1">
+        <v>46077</v>
+      </c>
+      <c r="J26">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>46087</v>
       </c>
@@ -4933,8 +7845,15 @@
       <c r="F27" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I27" s="1">
+        <v>46096</v>
+      </c>
+      <c r="J27">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>46044</v>
       </c>
@@ -4954,8 +7873,15 @@
       <c r="F28" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I28" s="1">
+        <v>46093</v>
+      </c>
+      <c r="J28">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>46053</v>
       </c>
@@ -4975,8 +7901,15 @@
       <c r="F29" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I29" s="1">
+        <v>46041</v>
+      </c>
+      <c r="J29">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>46112</v>
       </c>
@@ -4996,8 +7929,15 @@
       <c r="F30" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I30" s="1">
+        <v>46034</v>
+      </c>
+      <c r="J30">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>46040</v>
       </c>
@@ -5017,8 +7957,15 @@
       <c r="F31" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I31" s="1">
+        <v>46088</v>
+      </c>
+      <c r="J31">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>46105</v>
       </c>
@@ -5038,8 +7985,15 @@
       <c r="F32" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I32" s="1">
+        <v>46051</v>
+      </c>
+      <c r="J32">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>46088</v>
       </c>
@@ -5059,8 +8013,15 @@
       <c r="F33" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I33" s="1">
+        <v>46049</v>
+      </c>
+      <c r="J33">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>46048</v>
       </c>
@@ -5080,8 +8041,15 @@
       <c r="F34" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I34" s="1">
+        <v>46110</v>
+      </c>
+      <c r="J34">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>46077</v>
       </c>
@@ -5101,8 +8069,15 @@
       <c r="F35" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I35" s="1">
+        <v>46040</v>
+      </c>
+      <c r="J35">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>46053</v>
       </c>
@@ -5122,8 +8097,15 @@
       <c r="F36" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I36" s="1">
+        <v>46069</v>
+      </c>
+      <c r="J36">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>46111</v>
       </c>
@@ -5143,8 +8125,15 @@
       <c r="F37" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I37" s="1">
+        <v>46087</v>
+      </c>
+      <c r="J37">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>46054</v>
       </c>
@@ -5164,8 +8153,15 @@
       <c r="F38" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I38" s="1">
+        <v>46044</v>
+      </c>
+      <c r="J38">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>46034</v>
       </c>
@@ -5185,8 +8181,15 @@
       <c r="F39" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I39" s="1">
+        <v>46053</v>
+      </c>
+      <c r="J39">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>46057</v>
       </c>
@@ -5206,8 +8209,15 @@
       <c r="F40" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I40" s="1">
+        <v>46112</v>
+      </c>
+      <c r="J40">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>46054</v>
       </c>
@@ -5227,8 +8237,15 @@
       <c r="F41" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I41" s="1">
+        <v>46048</v>
+      </c>
+      <c r="J41">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>46103</v>
       </c>
@@ -5248,8 +8265,15 @@
       <c r="F42" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I42" s="1">
+        <v>46111</v>
+      </c>
+      <c r="J42">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>46112</v>
       </c>
@@ -5269,8 +8293,15 @@
       <c r="F43" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I43" s="1">
+        <v>46054</v>
+      </c>
+      <c r="J43">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>46074</v>
       </c>
@@ -5290,8 +8321,15 @@
       <c r="F44" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I44" s="1">
+        <v>46057</v>
+      </c>
+      <c r="J44">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>46045</v>
       </c>
@@ -5311,8 +8349,15 @@
       <c r="F45" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I45" s="1">
+        <v>46103</v>
+      </c>
+      <c r="J45">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>46093</v>
       </c>
@@ -5332,8 +8377,15 @@
       <c r="F46" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I46" s="1">
+        <v>46074</v>
+      </c>
+      <c r="J46">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>46082</v>
       </c>
@@ -5353,8 +8405,15 @@
       <c r="F47" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I47" s="1">
+        <v>46045</v>
+      </c>
+      <c r="J47">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>46043</v>
       </c>
@@ -5374,8 +8433,15 @@
       <c r="F48" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I48" s="1">
+        <v>46082</v>
+      </c>
+      <c r="J48">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>46083</v>
       </c>
@@ -5395,8 +8461,15 @@
       <c r="F49" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I49" s="1">
+        <v>46043</v>
+      </c>
+      <c r="J49">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>46103</v>
       </c>
@@ -5416,8 +8489,15 @@
       <c r="F50" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I50" s="1">
+        <v>46083</v>
+      </c>
+      <c r="J50">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>46043</v>
       </c>
@@ -5437,8 +8517,15 @@
       <c r="F51" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I51" s="1">
+        <v>46042</v>
+      </c>
+      <c r="J51">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>46042</v>
       </c>
@@ -5458,8 +8545,15 @@
       <c r="F52" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I52" s="1">
+        <v>46085</v>
+      </c>
+      <c r="J52">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>46044</v>
       </c>
@@ -5479,8 +8573,15 @@
       <c r="F53" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I53" s="1">
+        <v>46039</v>
+      </c>
+      <c r="J53">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>46085</v>
       </c>
@@ -5500,8 +8601,15 @@
       <c r="F54" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I54" s="1">
+        <v>46068</v>
+      </c>
+      <c r="J54">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>46039</v>
       </c>
@@ -5521,8 +8629,15 @@
       <c r="F55" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I55" s="1">
+        <v>46109</v>
+      </c>
+      <c r="J55">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>46068</v>
       </c>
@@ -5542,8 +8657,15 @@
       <c r="F56" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I56" s="1">
+        <v>46058</v>
+      </c>
+      <c r="J56">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>46109</v>
       </c>
@@ -5563,8 +8685,15 @@
       <c r="F57" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I57" s="1">
+        <v>46060</v>
+      </c>
+      <c r="J57">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>46069</v>
       </c>
@@ -5584,8 +8713,15 @@
       <c r="F58" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I58" s="1">
+        <v>46067</v>
+      </c>
+      <c r="J58">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>46083</v>
       </c>
@@ -5605,8 +8741,15 @@
       <c r="F59" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I59" s="1">
+        <v>46078</v>
+      </c>
+      <c r="J59">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>46058</v>
       </c>
@@ -5626,8 +8769,15 @@
       <c r="F60" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I60" s="1">
+        <v>46073</v>
+      </c>
+      <c r="J60">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>46060</v>
       </c>
@@ -5647,8 +8797,15 @@
       <c r="F61" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I61" s="1">
+        <v>46104</v>
+      </c>
+      <c r="J61">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>46067</v>
       </c>
@@ -5668,8 +8825,15 @@
       <c r="F62" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I62" s="1">
+        <v>46071</v>
+      </c>
+      <c r="J62">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>46078</v>
       </c>
@@ -5689,8 +8853,15 @@
       <c r="F63" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I63" s="1">
+        <v>46092</v>
+      </c>
+      <c r="J63">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>46040</v>
       </c>
@@ -5710,8 +8881,15 @@
       <c r="F64" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I64" s="1">
+        <v>46059</v>
+      </c>
+      <c r="J64">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>46051</v>
       </c>
@@ -5731,8 +8909,15 @@
       <c r="F65" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I65" s="1">
+        <v>46066</v>
+      </c>
+      <c r="J65">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>46073</v>
       </c>
@@ -5752,8 +8937,15 @@
       <c r="F66" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I66" s="1">
+        <v>46086</v>
+      </c>
+      <c r="J66">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>46104</v>
       </c>
@@ -5773,8 +8965,15 @@
       <c r="F67" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I67" s="1">
+        <v>46090</v>
+      </c>
+      <c r="J67">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>46071</v>
       </c>
@@ -5794,8 +8993,15 @@
       <c r="F68" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I68" s="1">
+        <v>46094</v>
+      </c>
+      <c r="J68">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>46092</v>
       </c>
@@ -5815,8 +9021,15 @@
       <c r="F69" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I69" s="1">
+        <v>46099</v>
+      </c>
+      <c r="J69">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>46059</v>
       </c>
@@ -5836,8 +9049,15 @@
       <c r="F70" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I70" s="1">
+        <v>46052</v>
+      </c>
+      <c r="J70">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>46111</v>
       </c>
@@ -5857,8 +9077,15 @@
       <c r="F71" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I71" s="1">
+        <v>46097</v>
+      </c>
+      <c r="J71">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>46096</v>
       </c>
@@ -5878,8 +9105,15 @@
       <c r="F72" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I72" s="1">
+        <v>46062</v>
+      </c>
+      <c r="J72">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>46105</v>
       </c>
@@ -5899,8 +9133,15 @@
       <c r="F73" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I73" s="1">
+        <v>46072</v>
+      </c>
+      <c r="J73">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>46066</v>
       </c>
@@ -5920,8 +9161,15 @@
       <c r="F74" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I74" s="1">
+        <v>46056</v>
+      </c>
+      <c r="J74">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>46086</v>
       </c>
@@ -5941,8 +9189,15 @@
       <c r="F75" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I75" s="1">
+        <v>46047</v>
+      </c>
+      <c r="J75">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>46044</v>
       </c>
@@ -5962,8 +9217,15 @@
       <c r="F76" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I76" s="1">
+        <v>46055</v>
+      </c>
+      <c r="J76">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>46090</v>
       </c>
@@ -5983,8 +9245,15 @@
       <c r="F77" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I77" s="1">
+        <v>46091</v>
+      </c>
+      <c r="J77">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>46068</v>
       </c>
@@ -6004,8 +9273,15 @@
       <c r="F78" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I78" s="1">
+        <v>46100</v>
+      </c>
+      <c r="J78">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>46110</v>
       </c>
@@ -6025,8 +9301,15 @@
       <c r="F79" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I79" s="1">
+        <v>46101</v>
+      </c>
+      <c r="J79">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>46061</v>
       </c>
@@ -6046,8 +9329,15 @@
       <c r="F80" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I80" s="1">
+        <v>46036</v>
+      </c>
+      <c r="J80">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>46094</v>
       </c>
@@ -6067,8 +9357,15 @@
       <c r="F81" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I81" s="1">
+        <v>46098</v>
+      </c>
+      <c r="J81">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>46083</v>
       </c>
@@ -6088,8 +9385,15 @@
       <c r="F82" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I82" s="1">
+        <v>46079</v>
+      </c>
+      <c r="J82">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>46099</v>
       </c>
@@ -6109,8 +9413,15 @@
       <c r="F83" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I83" s="1">
+        <v>46107</v>
+      </c>
+      <c r="J83">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>46037</v>
       </c>
@@ -6130,8 +9441,15 @@
       <c r="F84" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I84" s="1">
+        <v>46065</v>
+      </c>
+      <c r="J84">
+        <f t="shared" ref="J84:J90" si="2">COUNTIF($A$2:$A$10000,I84)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>46052</v>
       </c>
@@ -6151,8 +9469,15 @@
       <c r="F85" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I85" s="1">
+        <v>46064</v>
+      </c>
+      <c r="J85">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>46096</v>
       </c>
@@ -6172,8 +9497,15 @@
       <c r="F86" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I86" s="1">
+        <v>46038</v>
+      </c>
+      <c r="J86">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>46097</v>
       </c>
@@ -6193,8 +9525,15 @@
       <c r="F87" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I87" s="1">
+        <v>46084</v>
+      </c>
+      <c r="J87">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>46104</v>
       </c>
@@ -6214,8 +9553,15 @@
       <c r="F88" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I88" s="1">
+        <v>46106</v>
+      </c>
+      <c r="J88">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>46069</v>
       </c>
@@ -6235,8 +9581,15 @@
       <c r="F89" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I89" s="1">
+        <v>46046</v>
+      </c>
+      <c r="J89">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>46053</v>
       </c>
@@ -6256,8 +9609,15 @@
       <c r="F90" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I90" s="1">
+        <v>46076</v>
+      </c>
+      <c r="J90">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>46062</v>
       </c>
@@ -6278,7 +9638,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>46085</v>
       </c>
@@ -6299,7 +9659,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>46109</v>
       </c>
@@ -6320,7 +9680,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>46066</v>
       </c>
@@ -6341,7 +9701,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>46072</v>
       </c>
@@ -6362,7 +9722,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>46070</v>
       </c>
@@ -6383,7 +9743,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>46096</v>
       </c>
@@ -6404,7 +9764,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>46056</v>
       </c>
@@ -6425,7 +9785,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>46047</v>
       </c>
@@ -6446,7 +9806,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>46093</v>
       </c>
@@ -6467,7 +9827,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>46093</v>
       </c>
@@ -6488,7 +9848,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>46060</v>
       </c>
@@ -6509,7 +9869,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>46061</v>
       </c>
@@ -6530,7 +9890,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>46055</v>
       </c>
@@ -6551,7 +9911,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>46091</v>
       </c>
@@ -6572,7 +9932,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>46100</v>
       </c>
@@ -6593,7 +9953,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>46101</v>
       </c>
@@ -6614,7 +9974,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>46100</v>
       </c>
@@ -6635,7 +9995,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>46036</v>
       </c>
@@ -6656,7 +10016,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>46067</v>
       </c>
@@ -6677,7 +10037,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>46096</v>
       </c>
@@ -6698,7 +10058,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>46098</v>
       </c>
@@ -6719,7 +10079,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>46048</v>
       </c>
@@ -6740,7 +10100,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>46057</v>
       </c>
@@ -6761,7 +10121,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>46045</v>
       </c>
@@ -6782,7 +10142,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>46057</v>
       </c>
@@ -6803,7 +10163,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>46071</v>
       </c>
@@ -6824,7 +10184,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>46092</v>
       </c>
@@ -6845,7 +10205,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>46063</v>
       </c>
@@ -6866,7 +10226,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>46078</v>
       </c>
@@ -6887,7 +10247,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>46079</v>
       </c>
@@ -6908,7 +10268,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>46043</v>
       </c>
@@ -6929,7 +10289,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>46071</v>
       </c>
@@ -6950,7 +10310,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>46083</v>
       </c>
@@ -6971,7 +10331,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>46058</v>
       </c>
@@ -6992,7 +10352,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>46034</v>
       </c>
@@ -7013,7 +10373,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>46060</v>
       </c>
@@ -7034,7 +10394,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>46048</v>
       </c>
@@ -7055,7 +10415,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>46107</v>
       </c>
@@ -7076,7 +10436,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>46065</v>
       </c>
@@ -7097,7 +10457,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>46064</v>
       </c>
@@ -7118,7 +10478,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>46034</v>
       </c>
@@ -7139,7 +10499,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <v>46064</v>
       </c>
@@ -7160,7 +10520,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>46038</v>
       </c>
@@ -7181,7 +10541,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>46104</v>
       </c>
@@ -7202,7 +10562,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>46070</v>
       </c>
@@ -7223,7 +10583,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>46088</v>
       </c>
@@ -7244,7 +10604,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
         <v>46064</v>
       </c>
@@ -7265,7 +10625,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
         <v>46101</v>
       </c>
@@ -7286,7 +10646,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>46049</v>
       </c>
@@ -7307,7 +10667,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>46084</v>
       </c>
@@ -7328,7 +10688,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>46037</v>
       </c>
@@ -7349,7 +10709,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>46037</v>
       </c>
@@ -7370,7 +10730,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>46090</v>
       </c>
@@ -7391,7 +10751,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>46104</v>
       </c>
@@ -7412,7 +10772,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
         <v>46062</v>
       </c>
@@ -7433,7 +10793,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
         <v>46060</v>
       </c>
@@ -7454,7 +10814,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
         <v>46059</v>
       </c>
@@ -7475,7 +10835,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
         <v>46078</v>
       </c>
@@ -7496,7 +10856,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
         <v>46111</v>
       </c>
@@ -7517,7 +10877,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
         <v>46039</v>
       </c>
@@ -7538,7 +10898,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
         <v>46091</v>
       </c>
@@ -7559,7 +10919,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
         <v>46106</v>
       </c>
@@ -7580,7 +10940,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>46051</v>
       </c>
@@ -7601,7 +10961,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>46103</v>
       </c>
@@ -7622,7 +10982,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>46068</v>
       </c>
@@ -7643,7 +11003,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
         <v>46046</v>
       </c>
@@ -7664,7 +11024,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>46090</v>
       </c>
@@ -7685,7 +11045,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>46101</v>
       </c>
@@ -7706,7 +11066,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>46091</v>
       </c>
@@ -7727,7 +11087,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
         <v>46109</v>
       </c>
@@ -7748,7 +11108,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A162" s="1">
         <v>46062</v>
       </c>
@@ -7769,7 +11129,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A163" s="1">
         <v>46067</v>
       </c>
@@ -7790,7 +11150,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A164" s="1">
         <v>46065</v>
       </c>
@@ -7811,7 +11171,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A165" s="1">
         <v>46041</v>
       </c>
@@ -7832,7 +11192,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A166" s="1">
         <v>46073</v>
       </c>
@@ -7853,7 +11213,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A167" s="1">
         <v>46059</v>
       </c>
@@ -7874,7 +11234,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
         <v>46086</v>
       </c>
@@ -7895,7 +11255,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A169" s="1">
         <v>46060</v>
       </c>
@@ -7916,7 +11276,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A170" s="1">
         <v>46076</v>
       </c>
@@ -7937,7 +11297,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A171" s="1">
         <v>46108</v>
       </c>
@@ -7958,7 +11318,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A172" s="1">
         <v>46043</v>
       </c>
@@ -7979,7 +11339,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A173" s="1">
         <v>46079</v>
       </c>
@@ -8000,7 +11360,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A174" s="1">
         <v>46088</v>
       </c>
@@ -8021,7 +11381,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A175" s="1">
         <v>46077</v>
       </c>
@@ -8055,15 +11415,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94D34C61-9FDE-4A5D-BAAC-4B916634F076}">
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -8077,7 +11437,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="str" cm="1">
         <f t="array" ref="A2:A8">_xlfn.UNIQUE(Base!B2:B175)</f>
         <v>Roberto</v>
@@ -8095,7 +11455,7 @@
         <v>906.13636363636363</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
         <v>Adão</v>
       </c>
@@ -8112,7 +11472,7 @@
         <v>841.44444444444446</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
         <v>Chaga</v>
       </c>
@@ -8129,7 +11489,7 @@
         <v>847.27586206896547</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="str">
         <v>Erisvaldo</v>
       </c>
@@ -8146,7 +11506,7 @@
         <v>852.43478260869563</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <v>Emanuel</v>
       </c>
@@ -8163,7 +11523,7 @@
         <v>863.33333333333337</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <v>Julio</v>
       </c>
@@ -8180,7 +11540,7 @@
         <v>819.33333333333337</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="str">
         <v>Carlos</v>
       </c>
@@ -8205,13 +11565,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38AB050B-83A9-4641-9396-FC0189DB5392}">
   <dimension ref="A3:B8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>28</v>
       </c>
@@ -8219,7 +11579,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>16</v>
       </c>
@@ -8227,7 +11587,7 @@
         <v>26530700</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>14</v>
       </c>
@@ -8235,7 +11595,7 @@
         <v>14040800</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>13</v>
       </c>
@@ -8243,7 +11603,7 @@
         <v>4444500</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>15</v>
       </c>
@@ -8251,7 +11611,7 @@
         <v>3721920</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>29</v>
       </c>
@@ -8267,14 +11627,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5569F8BE-AD8E-48AD-B078-D4E4B9D8347B}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.90625" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.7265625" style="7" customWidth="1"/>
-    <col min="3" max="16384" width="8.7265625" style="7"/>
+    <col min="1" max="1" width="21.88671875" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.77734375" style="7" customWidth="1"/>
+    <col min="3" max="16384" width="8.77734375" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
         <v>31</v>
       </c>
@@ -8283,7 +11643,7 @@
         <v>Campinas</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="15" t="s">
         <v>32</v>
       </c>
@@ -8292,7 +11652,7 @@
         <v>Emanuel</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>33</v>
       </c>
@@ -8302,7 +11662,7 @@
       </c>
       <c r="D3" s="8"/>
     </row>
-    <row r="4" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
         <v>34</v>
       </c>
@@ -8311,7 +11671,7 @@
         <v>0.35057471264367818</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="5" spans="1:4" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -8319,12 +11679,282 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87C2F01C-AC01-4C42-B465-4F99E404F8DC}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AB16"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" width="8.7265625" style="6"/>
+    <col min="1" max="1" width="8.77734375" style="6"/>
+    <col min="2" max="2" width="20.21875" style="6" customWidth="1"/>
+    <col min="3" max="14" width="8.77734375" style="6"/>
+    <col min="15" max="15" width="12.44140625" style="6" customWidth="1"/>
+    <col min="16" max="16384" width="8.77734375" style="6"/>
   </cols>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:28" s="28" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="29"/>
+      <c r="N1" s="29"/>
+      <c r="O1" s="29"/>
+      <c r="P1" s="29"/>
+      <c r="Q1" s="29"/>
+      <c r="R1" s="29"/>
+      <c r="S1" s="29"/>
+      <c r="T1" s="29"/>
+      <c r="U1" s="29"/>
+      <c r="V1" s="29"/>
+      <c r="W1" s="29"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="31"/>
+      <c r="Z1" s="31"/>
+      <c r="AA1" s="31"/>
+      <c r="AB1" s="31"/>
+    </row>
+    <row r="2" spans="1:28" s="28" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="29"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="29"/>
+      <c r="N2" s="29"/>
+      <c r="O2" s="29"/>
+      <c r="P2" s="29"/>
+      <c r="Q2" s="29"/>
+      <c r="R2" s="29"/>
+      <c r="S2" s="29"/>
+      <c r="T2" s="29"/>
+      <c r="U2" s="29"/>
+      <c r="V2" s="29"/>
+      <c r="W2" s="29"/>
+      <c r="X2" s="29"/>
+      <c r="Y2" s="31"/>
+      <c r="Z2" s="31"/>
+      <c r="AA2" s="31"/>
+      <c r="AB2" s="31"/>
+    </row>
+    <row r="3" spans="1:28" s="28" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="29"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
+      <c r="J3" s="29"/>
+      <c r="K3" s="29"/>
+      <c r="L3" s="29"/>
+      <c r="M3" s="29"/>
+      <c r="N3" s="29"/>
+      <c r="O3" s="29"/>
+      <c r="P3" s="29"/>
+      <c r="Q3" s="29"/>
+      <c r="R3" s="29"/>
+      <c r="S3" s="29"/>
+      <c r="T3" s="29"/>
+      <c r="U3" s="29"/>
+      <c r="V3" s="29"/>
+      <c r="W3" s="29"/>
+      <c r="X3" s="29"/>
+      <c r="Y3" s="31"/>
+      <c r="Z3" s="31"/>
+      <c r="AA3" s="31"/>
+      <c r="AB3" s="31"/>
+    </row>
+    <row r="4" spans="1:28" s="28" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="29"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
+      <c r="K4" s="29"/>
+      <c r="L4" s="29"/>
+      <c r="M4" s="29"/>
+      <c r="N4" s="29"/>
+      <c r="O4" s="29"/>
+      <c r="P4" s="29"/>
+      <c r="Q4" s="29"/>
+      <c r="R4" s="29"/>
+      <c r="S4" s="29"/>
+      <c r="T4" s="29"/>
+      <c r="U4" s="29"/>
+      <c r="V4" s="29"/>
+      <c r="W4" s="29"/>
+      <c r="X4" s="29"/>
+      <c r="Y4" s="31"/>
+      <c r="Z4" s="31"/>
+      <c r="AA4" s="31"/>
+      <c r="AB4" s="31"/>
+    </row>
+    <row r="5" spans="1:28" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="28"/>
+      <c r="B5" s="30" t="str">
+        <f>Painel!A1</f>
+        <v>Cidade Campeã</v>
+      </c>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30" t="str">
+        <f>Painel!A2</f>
+        <v>Motorista Destaque</v>
+      </c>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="30"/>
+      <c r="J5" s="30"/>
+      <c r="K5" s="30" t="str">
+        <f>Painel!A3</f>
+        <v>Maior Frete(R$)</v>
+      </c>
+      <c r="L5" s="30"/>
+      <c r="M5" s="30"/>
+      <c r="N5" s="30"/>
+      <c r="O5" s="30"/>
+      <c r="P5" s="30" t="str">
+        <f>Painel!A4</f>
+        <v>% de Entregas Concluídas</v>
+      </c>
+      <c r="Q5" s="30"/>
+      <c r="R5" s="30"/>
+      <c r="S5" s="30"/>
+      <c r="T5" s="30"/>
+      <c r="U5" s="30"/>
+      <c r="V5" s="30"/>
+      <c r="W5" s="28"/>
+      <c r="X5" s="28"/>
+      <c r="Y5" s="28"/>
+      <c r="Z5" s="28"/>
+      <c r="AA5" s="28"/>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="B6" s="33" t="str">
+        <f>Painel!B1</f>
+        <v>Campinas</v>
+      </c>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="33" t="str">
+        <f>Painel!B2</f>
+        <v>Emanuel</v>
+      </c>
+      <c r="G6" s="34"/>
+      <c r="H6" s="34"/>
+      <c r="I6" s="34"/>
+      <c r="J6" s="35"/>
+      <c r="K6" s="42">
+        <f>Painel!B3</f>
+        <v>823900</v>
+      </c>
+      <c r="L6" s="43"/>
+      <c r="M6" s="43"/>
+      <c r="N6" s="43"/>
+      <c r="O6" s="44"/>
+      <c r="P6" s="45">
+        <f>Painel!B4</f>
+        <v>0.35057471264367818</v>
+      </c>
+      <c r="Q6" s="34"/>
+      <c r="R6" s="34"/>
+      <c r="S6" s="34"/>
+      <c r="T6" s="34"/>
+      <c r="U6" s="34"/>
+      <c r="V6" s="35"/>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="B7" s="36"/>
+      <c r="C7" s="37"/>
+      <c r="D7" s="37"/>
+      <c r="E7" s="38"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="37"/>
+      <c r="H7" s="37"/>
+      <c r="I7" s="37"/>
+      <c r="J7" s="38"/>
+      <c r="K7" s="46"/>
+      <c r="L7" s="47"/>
+      <c r="M7" s="47"/>
+      <c r="N7" s="47"/>
+      <c r="O7" s="48"/>
+      <c r="P7" s="36"/>
+      <c r="Q7" s="37"/>
+      <c r="R7" s="37"/>
+      <c r="S7" s="37"/>
+      <c r="T7" s="37"/>
+      <c r="U7" s="37"/>
+      <c r="V7" s="38"/>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="B8" s="39"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="40"/>
+      <c r="J8" s="41"/>
+      <c r="K8" s="49"/>
+      <c r="L8" s="50"/>
+      <c r="M8" s="50"/>
+      <c r="N8" s="50"/>
+      <c r="O8" s="51"/>
+      <c r="P8" s="39"/>
+      <c r="Q8" s="40"/>
+      <c r="R8" s="40"/>
+      <c r="S8" s="40"/>
+      <c r="T8" s="40"/>
+      <c r="U8" s="40"/>
+      <c r="V8" s="41"/>
+    </row>
+    <row r="9" spans="1:28" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A11" s="52"/>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="J15" s="32"/>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="J16" s="32"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="P5:V5"/>
+    <mergeCell ref="A1:X4"/>
+    <mergeCell ref="B6:E8"/>
+    <mergeCell ref="F6:J8"/>
+    <mergeCell ref="K6:O8"/>
+    <mergeCell ref="P6:V8"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="F5:J5"/>
+    <mergeCell ref="K5:O5"/>
+  </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <drawing r:id="rId1"/>
 </worksheet>
